--- a/PPG/Destaques.xlsx
+++ b/PPG/Destaques.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0638E084-158F-CC41-A3AC-91DFF5B19F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3125854-A7EE-4349-BBCE-6C6D78F25750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="980" yWindow="680" windowWidth="27500" windowHeight="16900" xr2:uid="{532D0FCC-2B74-AC48-A173-8BCE0F3E070A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="95">
   <si>
     <t>Documento</t>
   </si>
@@ -303,6 +303,24 @@
   </si>
   <si>
     <t>https://mpsm.ufsc.br/2025/12/19/chamada-publica-no-012025-para-credenciamento-docente-do-mpsm-20262028/</t>
+  </si>
+  <si>
+    <t>https://youtu.be/CNVOeEZJ-JM</t>
+  </si>
+  <si>
+    <t>Second WHO Global Summit on Traditional Medicine | 17-19 December 2025 - New Delhi, India</t>
+  </si>
+  <si>
+    <t>https://prossim.uerj.br/selecoes/selecao_1561/pontuacao_e_resultados_1561_1772822292.pdf</t>
+  </si>
+  <si>
+    <t>CONCURSO PÚBLICO PARA PROVIMENTO DE CARGO DE PROFESSOR ADJUNTO – 40H - ÁREA: FISIOTERAPIA COM ÊNFASE EM SAÚDE COLETIVA RESULTADO FINAL - 06 DE MARÇO DE 20226 - Juliana Valentim Bittencourt 2ª Colocada</t>
+  </si>
+  <si>
+    <t>https://cdn.who.int/media/docs/default-source/who-global-traditional-medicine-centre/h2i/neonatal-osteopathic-care-uk.pdf?sfvrsn=aa8a3294_1</t>
+  </si>
+  <si>
+    <t>Neonatal osteopathic care Integrating neonatal osteopathic care with global implementation protocols to improve health and economic outcomes</t>
   </si>
 </sst>
 </file>
@@ -711,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4ABEF7-94C4-7247-BD80-8BBBAECAE311}">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="8" bestFit="1" customWidth="1"/>
@@ -1239,24 +1257,66 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+      <c r="A39" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B39" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D38" s="4" t="s">
+      <c r="C39" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>85</v>
       </c>
     </row>
+    <row r="40" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A40" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A41" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D38">
-    <sortCondition ref="A2:A38"/>
-    <sortCondition ref="B2:B38"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D39">
+    <sortCondition ref="A2:A39"/>
+    <sortCondition ref="B2:B39"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="D14" r:id="rId1" xr:uid="{DFF238BA-4FD8-F240-9DF9-E466F5842315}"/>
@@ -1294,8 +1354,11 @@
     <hyperlink ref="D29" r:id="rId33" xr:uid="{3B1BE636-2D48-9046-8ACB-F8255380A361}"/>
     <hyperlink ref="D24" r:id="rId34" xr:uid="{C0AAAFD9-4A51-FE4E-ACCC-DF3E0086CCE9}"/>
     <hyperlink ref="D5" r:id="rId35" xr:uid="{CBF5A22B-A747-014F-9236-71EF22A462E5}"/>
-    <hyperlink ref="D38" r:id="rId36" xr:uid="{E2D6568A-D482-AF4D-B1A9-813FBC4D158C}"/>
+    <hyperlink ref="D39" r:id="rId36" xr:uid="{E2D6568A-D482-AF4D-B1A9-813FBC4D158C}"/>
     <hyperlink ref="D25" r:id="rId37" xr:uid="{C5A02E17-A8D8-1942-893A-EA616748851F}"/>
+    <hyperlink ref="D38" r:id="rId38" xr:uid="{FA581FA2-B28D-2147-B223-7E15CA5B2972}"/>
+    <hyperlink ref="D40" r:id="rId39" xr:uid="{A4905BDD-5388-7A4C-984D-D088085D95E1}"/>
+    <hyperlink ref="D41" r:id="rId40" xr:uid="{81717D2E-9A06-E74D-807A-BEA54DE45F31}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/PPG/Destaques.xlsx
+++ b/PPG/Destaques.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3125854-A7EE-4349-BBCE-6C6D78F25750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63102DD0-0346-0640-9124-8F8E1F9AD1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="980" yWindow="680" windowWidth="27500" windowHeight="16900" xr2:uid="{532D0FCC-2B74-AC48-A173-8BCE0F3E070A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="97">
   <si>
     <t>Documento</t>
   </si>
@@ -321,6 +321,12 @@
   </si>
   <si>
     <t>Neonatal osteopathic care Integrating neonatal osteopathic care with global implementation protocols to improve health and economic outcomes</t>
+  </si>
+  <si>
+    <t>https://www.ufrb.edu.br/ppgecid/noticias/542-resultado-parcial-do-edital-de-credenciamento-docente</t>
+  </si>
+  <si>
+    <t>A Comissão Temporária de Credenciamento, Recredenciamento e Descredenciamento do Programa de Pós-Graduação em Educação Científica, Inclusão e Diversidade (PPGECID) desta Universidade, no uso das suas atribuições, torna público o resultado do Edital de Credenciamento docente.</t>
   </si>
 </sst>
 </file>
@@ -729,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4ABEF7-94C4-7247-BD80-8BBBAECAE311}">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="8" bestFit="1" customWidth="1"/>
@@ -1311,6 +1317,20 @@
       </c>
       <c r="D41" s="4" t="s">
         <v>93</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A42" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1359,6 +1379,7 @@
     <hyperlink ref="D38" r:id="rId38" xr:uid="{FA581FA2-B28D-2147-B223-7E15CA5B2972}"/>
     <hyperlink ref="D40" r:id="rId39" xr:uid="{A4905BDD-5388-7A4C-984D-D088085D95E1}"/>
     <hyperlink ref="D41" r:id="rId40" xr:uid="{81717D2E-9A06-E74D-807A-BEA54DE45F31}"/>
+    <hyperlink ref="D42" r:id="rId41" xr:uid="{A83BF367-BB20-EC40-A883-8D6769B3145A}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
